--- a/output/yearly_population_iteration_67_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_67_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4838</v>
+        <v>6069</v>
       </c>
       <c r="C2" t="n">
-        <v>8383</v>
+        <v>14703</v>
       </c>
       <c r="D2" t="n">
-        <v>38444</v>
+        <v>24382</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3596</v>
+        <v>3456</v>
       </c>
       <c r="C3" t="n">
-        <v>6058</v>
+        <v>6700</v>
       </c>
       <c r="D3" t="n">
-        <v>21834</v>
+        <v>10476</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2926</v>
+        <v>2567</v>
       </c>
       <c r="C4" t="n">
-        <v>6005</v>
+        <v>6809</v>
       </c>
       <c r="D4" t="n">
-        <v>9332</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1843</v>
+        <v>1756</v>
       </c>
       <c r="C5" t="n">
-        <v>5116</v>
+        <v>6230</v>
       </c>
       <c r="D5" t="n">
-        <v>2822</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1038</v>
+        <v>1060</v>
       </c>
       <c r="C6" t="n">
-        <v>4205</v>
+        <v>4020</v>
       </c>
       <c r="D6" t="n">
-        <v>1089</v>
+        <v>945</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="C7" t="n">
-        <v>2861</v>
+        <v>2355</v>
       </c>
       <c r="D7" t="n">
-        <v>619</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="C8" t="n">
-        <v>1425</v>
+        <v>1154</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>521</v>
+        <v>457</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5449</v>
+        <v>7003</v>
       </c>
       <c r="C2" t="n">
-        <v>15875</v>
+        <v>13298</v>
       </c>
       <c r="D2" t="n">
-        <v>30686</v>
+        <v>31047</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3370</v>
+        <v>3708</v>
       </c>
       <c r="C3" t="n">
-        <v>6216</v>
+        <v>8990</v>
       </c>
       <c r="D3" t="n">
-        <v>22429</v>
+        <v>11568</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2759</v>
+        <v>2511</v>
       </c>
       <c r="C4" t="n">
-        <v>5845</v>
+        <v>6551</v>
       </c>
       <c r="D4" t="n">
-        <v>10759</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2004</v>
+        <v>1858</v>
       </c>
       <c r="C5" t="n">
-        <v>5385</v>
+        <v>6361</v>
       </c>
       <c r="D5" t="n">
-        <v>3673</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1229</v>
+        <v>1243</v>
       </c>
       <c r="C6" t="n">
-        <v>4494</v>
+        <v>4897</v>
       </c>
       <c r="D6" t="n">
-        <v>1297</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>623</v>
+        <v>647</v>
       </c>
       <c r="C7" t="n">
-        <v>3371</v>
+        <v>3072</v>
       </c>
       <c r="D7" t="n">
-        <v>671</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="C8" t="n">
-        <v>1987</v>
+        <v>1636</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C9" t="n">
-        <v>852</v>
+        <v>732</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5638</v>
+        <v>8556</v>
       </c>
       <c r="C2" t="n">
-        <v>11033</v>
+        <v>14415</v>
       </c>
       <c r="D2" t="n">
-        <v>34345</v>
+        <v>35367</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3377</v>
+        <v>4038</v>
       </c>
       <c r="C3" t="n">
-        <v>8727</v>
+        <v>9600</v>
       </c>
       <c r="D3" t="n">
-        <v>21954</v>
+        <v>13165</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2551</v>
+        <v>2527</v>
       </c>
       <c r="C4" t="n">
-        <v>5813</v>
+        <v>7358</v>
       </c>
       <c r="D4" t="n">
-        <v>11897</v>
+        <v>6016</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2034</v>
+        <v>1881</v>
       </c>
       <c r="C5" t="n">
-        <v>5449</v>
+        <v>6244</v>
       </c>
       <c r="D5" t="n">
-        <v>4513</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1376</v>
+        <v>1353</v>
       </c>
       <c r="C6" t="n">
-        <v>4739</v>
+        <v>5383</v>
       </c>
       <c r="D6" t="n">
-        <v>1564</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>754</v>
+        <v>785</v>
       </c>
       <c r="C7" t="n">
-        <v>3743</v>
+        <v>3786</v>
       </c>
       <c r="D7" t="n">
-        <v>743</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="C8" t="n">
-        <v>2455</v>
+        <v>2154</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C9" t="n">
-        <v>1240</v>
+        <v>1052</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5351</v>
+        <v>7816</v>
       </c>
       <c r="C2" t="n">
-        <v>7943</v>
+        <v>10148</v>
       </c>
       <c r="D2" t="n">
-        <v>28740</v>
+        <v>28925</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4216</v>
+        <v>4630</v>
       </c>
       <c r="C3" t="n">
-        <v>11883</v>
+        <v>13778</v>
       </c>
       <c r="D3" t="n">
-        <v>23580</v>
+        <v>13854</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1879</v>
+        <v>1738</v>
       </c>
       <c r="C4" t="n">
-        <v>8188</v>
+        <v>9879</v>
       </c>
       <c r="D4" t="n">
-        <v>10814</v>
+        <v>5647</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1271</v>
+        <v>1250</v>
       </c>
       <c r="C5" t="n">
-        <v>4644</v>
+        <v>5275</v>
       </c>
       <c r="D5" t="n">
-        <v>2702</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>696</v>
+        <v>725</v>
       </c>
       <c r="C6" t="n">
-        <v>3668</v>
+        <v>3710</v>
       </c>
       <c r="D6" t="n">
-        <v>728</v>
+        <v>679</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="C7" t="n">
-        <v>2405</v>
+        <v>2110</v>
       </c>
       <c r="D7" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>1215</v>
+        <v>1030</v>
       </c>
       <c r="D8" t="n">
-        <v>313</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>486</v>
+        <v>453</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>37</v>
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3464</v>
+        <v>4625</v>
       </c>
       <c r="C2" t="n">
-        <v>5097</v>
+        <v>5072</v>
       </c>
       <c r="D2" t="n">
-        <v>19722</v>
+        <v>21495</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4062</v>
+        <v>5081</v>
       </c>
       <c r="C3" t="n">
-        <v>9324</v>
+        <v>11069</v>
       </c>
       <c r="D3" t="n">
-        <v>23146</v>
+        <v>15007</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2362</v>
+        <v>2427</v>
       </c>
       <c r="C4" t="n">
-        <v>9928</v>
+        <v>11812</v>
       </c>
       <c r="D4" t="n">
-        <v>12304</v>
+        <v>6765</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1409</v>
+        <v>1371</v>
       </c>
       <c r="C5" t="n">
-        <v>6097</v>
+        <v>7230</v>
       </c>
       <c r="D5" t="n">
-        <v>3606</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>801</v>
+        <v>848</v>
       </c>
       <c r="C6" t="n">
-        <v>4158</v>
+        <v>4412</v>
       </c>
       <c r="D6" t="n">
-        <v>911</v>
+        <v>789</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="C7" t="n">
-        <v>2889</v>
+        <v>2702</v>
       </c>
       <c r="D7" t="n">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>1573</v>
+        <v>1339</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D9" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3894</v>
+        <v>3954</v>
       </c>
       <c r="C2" t="n">
-        <v>12380</v>
+        <v>6964</v>
       </c>
       <c r="D2" t="n">
-        <v>15429</v>
+        <v>19865</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3254</v>
+        <v>4114</v>
       </c>
       <c r="C3" t="n">
-        <v>6701</v>
+        <v>7448</v>
       </c>
       <c r="D3" t="n">
-        <v>21189</v>
+        <v>15024</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2603</v>
+        <v>3034</v>
       </c>
       <c r="C4" t="n">
-        <v>9448</v>
+        <v>11216</v>
       </c>
       <c r="D4" t="n">
-        <v>13595</v>
+        <v>7760</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1596</v>
+        <v>1601</v>
       </c>
       <c r="C5" t="n">
-        <v>7625</v>
+        <v>9147</v>
       </c>
       <c r="D5" t="n">
-        <v>4748</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>947</v>
+        <v>971</v>
       </c>
       <c r="C6" t="n">
-        <v>4920</v>
+        <v>5631</v>
       </c>
       <c r="D6" t="n">
-        <v>1261</v>
+        <v>988</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>418</v>
+        <v>453</v>
       </c>
       <c r="C7" t="n">
-        <v>3426</v>
+        <v>3431</v>
       </c>
       <c r="D7" t="n">
-        <v>540</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C8" t="n">
-        <v>2077</v>
+        <v>1872</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>866</v>
+        <v>793</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>35</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2380</v>
+        <v>2403</v>
       </c>
       <c r="C2" t="n">
-        <v>6156</v>
+        <v>3428</v>
       </c>
       <c r="D2" t="n">
-        <v>10880</v>
+        <v>14009</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3305</v>
+        <v>3973</v>
       </c>
       <c r="C3" t="n">
-        <v>8266</v>
+        <v>7034</v>
       </c>
       <c r="D3" t="n">
-        <v>20195</v>
+        <v>15176</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2834</v>
+        <v>3295</v>
       </c>
       <c r="C4" t="n">
-        <v>9367</v>
+        <v>11009</v>
       </c>
       <c r="D4" t="n">
-        <v>14508</v>
+        <v>8509</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1651</v>
+        <v>1674</v>
       </c>
       <c r="C5" t="n">
-        <v>9240</v>
+        <v>11004</v>
       </c>
       <c r="D5" t="n">
-        <v>4876</v>
+        <v>2965</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>744</v>
+        <v>795</v>
       </c>
       <c r="C6" t="n">
-        <v>5742</v>
+        <v>6517</v>
       </c>
       <c r="D6" t="n">
-        <v>1225</v>
+        <v>980</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="C7" t="n">
-        <v>3614</v>
+        <v>3488</v>
       </c>
       <c r="D7" t="n">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1418</v>
+        <v>1309</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>34</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3030</v>
+        <v>2644</v>
       </c>
       <c r="C2" t="n">
-        <v>11137</v>
+        <v>5955</v>
       </c>
       <c r="D2" t="n">
-        <v>14982</v>
+        <v>15532</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2525</v>
+        <v>2882</v>
       </c>
       <c r="C3" t="n">
-        <v>6599</v>
+        <v>4895</v>
       </c>
       <c r="D3" t="n">
-        <v>17871</v>
+        <v>14031</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2631</v>
+        <v>3105</v>
       </c>
       <c r="C4" t="n">
-        <v>8775</v>
+        <v>9092</v>
       </c>
       <c r="D4" t="n">
-        <v>14885</v>
+        <v>9274</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1879</v>
+        <v>2037</v>
       </c>
       <c r="C5" t="n">
-        <v>9100</v>
+        <v>10777</v>
       </c>
       <c r="D5" t="n">
-        <v>6022</v>
+        <v>3701</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>964</v>
+        <v>1014</v>
       </c>
       <c r="C6" t="n">
-        <v>7181</v>
+        <v>8396</v>
       </c>
       <c r="D6" t="n">
-        <v>1664</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="C7" t="n">
-        <v>4419</v>
+        <v>4648</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>2176</v>
+        <v>2081</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>644</v>
+        <v>624</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>32</v>
@@ -3159,7 +3159,7 @@
         <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1997</v>
+        <v>1811</v>
       </c>
       <c r="C2" t="n">
-        <v>6250</v>
+        <v>5056</v>
       </c>
       <c r="D2" t="n">
-        <v>12286</v>
+        <v>12359</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2346</v>
+        <v>2465</v>
       </c>
       <c r="C3" t="n">
-        <v>7517</v>
+        <v>4867</v>
       </c>
       <c r="D3" t="n">
-        <v>16775</v>
+        <v>13458</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2396</v>
+        <v>2803</v>
       </c>
       <c r="C4" t="n">
-        <v>8030</v>
+        <v>7506</v>
       </c>
       <c r="D4" t="n">
-        <v>14919</v>
+        <v>9674</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1988</v>
+        <v>2204</v>
       </c>
       <c r="C5" t="n">
-        <v>9154</v>
+        <v>10400</v>
       </c>
       <c r="D5" t="n">
-        <v>6747</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1090</v>
+        <v>1170</v>
       </c>
       <c r="C6" t="n">
-        <v>8005</v>
+        <v>9418</v>
       </c>
       <c r="D6" t="n">
-        <v>2027</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>5245</v>
+        <v>5773</v>
       </c>
       <c r="D7" t="n">
-        <v>687</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2703</v>
+        <v>2633</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>675</v>
+        <v>661</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>36</v>
+      </c>
+      <c r="D14" t="n">
         <v>35</v>
-      </c>
-      <c r="D14" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2873</v>
+        <v>2644</v>
       </c>
       <c r="C2" t="n">
-        <v>17555</v>
+        <v>5015</v>
       </c>
       <c r="D2" t="n">
-        <v>10807</v>
+        <v>16332</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1882</v>
+        <v>1899</v>
       </c>
       <c r="C3" t="n">
-        <v>6379</v>
+        <v>4455</v>
       </c>
       <c r="D3" t="n">
-        <v>15225</v>
+        <v>12495</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2088</v>
+        <v>2340</v>
       </c>
       <c r="C4" t="n">
-        <v>7588</v>
+        <v>6311</v>
       </c>
       <c r="D4" t="n">
-        <v>14714</v>
+        <v>9888</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1934</v>
+        <v>2186</v>
       </c>
       <c r="C5" t="n">
-        <v>8542</v>
+        <v>9000</v>
       </c>
       <c r="D5" t="n">
-        <v>7561</v>
+        <v>4796</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1269</v>
+        <v>1390</v>
       </c>
       <c r="C6" t="n">
-        <v>8350</v>
+        <v>9793</v>
       </c>
       <c r="D6" t="n">
-        <v>2545</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>417</v>
+        <v>462</v>
       </c>
       <c r="C7" t="n">
-        <v>6240</v>
+        <v>7020</v>
       </c>
       <c r="D7" t="n">
-        <v>824</v>
+        <v>727</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>3499</v>
+        <v>3647</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>1277</v>
+        <v>1266</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6902</v>
+        <v>5969</v>
       </c>
       <c r="C2" t="n">
-        <v>16862</v>
+        <v>11770</v>
       </c>
       <c r="D2" t="n">
-        <v>7111</v>
+        <v>4156</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2120</v>
+        <v>1954</v>
       </c>
       <c r="C2" t="n">
-        <v>10533</v>
+        <v>2969</v>
       </c>
       <c r="D2" t="n">
-        <v>8126</v>
+        <v>12151</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2516</v>
+        <v>2584</v>
       </c>
       <c r="C3" t="n">
-        <v>9424</v>
+        <v>5098</v>
       </c>
       <c r="D3" t="n">
-        <v>16264</v>
+        <v>13669</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2836</v>
+        <v>3216</v>
       </c>
       <c r="C4" t="n">
-        <v>10446</v>
+        <v>9303</v>
       </c>
       <c r="D4" t="n">
-        <v>14882</v>
+        <v>9930</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1172</v>
+        <v>1284</v>
       </c>
       <c r="C5" t="n">
-        <v>12121</v>
+        <v>13581</v>
       </c>
       <c r="D5" t="n">
-        <v>6643</v>
+        <v>4261</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="C6" t="n">
-        <v>7424</v>
+        <v>8511</v>
       </c>
       <c r="D6" t="n">
-        <v>1932</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>3429</v>
+        <v>3574</v>
       </c>
       <c r="D7" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>1251</v>
+        <v>1240</v>
       </c>
       <c r="D8" t="n">
-        <v>280</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D9" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6627</v>
+        <v>6849</v>
       </c>
       <c r="C2" t="n">
-        <v>10989</v>
+        <v>6589</v>
       </c>
       <c r="D2" t="n">
-        <v>10055</v>
+        <v>6061</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2932</v>
+        <v>2536</v>
       </c>
       <c r="C3" t="n">
-        <v>8498</v>
+        <v>5932</v>
       </c>
       <c r="D3" t="n">
-        <v>1833</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6351</v>
+        <v>5492</v>
       </c>
       <c r="C2" t="n">
-        <v>5114</v>
+        <v>6794</v>
       </c>
       <c r="D2" t="n">
-        <v>25289</v>
+        <v>13619</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3927</v>
+        <v>3853</v>
       </c>
       <c r="C3" t="n">
-        <v>8544</v>
+        <v>5436</v>
       </c>
       <c r="D3" t="n">
-        <v>3079</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1308</v>
+        <v>1135</v>
       </c>
       <c r="C4" t="n">
-        <v>5022</v>
+        <v>3517</v>
       </c>
       <c r="D4" t="n">
-        <v>1550</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5225</v>
+        <v>5151</v>
       </c>
       <c r="C2" t="n">
-        <v>9400</v>
+        <v>9162</v>
       </c>
       <c r="D2" t="n">
-        <v>37051</v>
+        <v>15434</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4178</v>
+        <v>3827</v>
       </c>
       <c r="C3" t="n">
-        <v>5817</v>
+        <v>5346</v>
       </c>
       <c r="D3" t="n">
-        <v>6410</v>
+        <v>3739</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2196</v>
+        <v>2121</v>
       </c>
       <c r="C4" t="n">
-        <v>6878</v>
+        <v>4530</v>
       </c>
       <c r="D4" t="n">
-        <v>1796</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>587</v>
+        <v>516</v>
       </c>
       <c r="C5" t="n">
-        <v>2799</v>
+        <v>2019</v>
       </c>
       <c r="D5" t="n">
-        <v>1225</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5992</v>
+        <v>5534</v>
       </c>
       <c r="C2" t="n">
-        <v>7107</v>
+        <v>11733</v>
       </c>
       <c r="D2" t="n">
-        <v>41214</v>
+        <v>17678</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3838</v>
+        <v>3697</v>
       </c>
       <c r="C3" t="n">
-        <v>6629</v>
+        <v>6362</v>
       </c>
       <c r="D3" t="n">
-        <v>10381</v>
+        <v>5253</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2649</v>
+        <v>2493</v>
       </c>
       <c r="C4" t="n">
-        <v>6184</v>
+        <v>4874</v>
       </c>
       <c r="D4" t="n">
-        <v>2521</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1137</v>
+        <v>1080</v>
       </c>
       <c r="C5" t="n">
-        <v>4750</v>
+        <v>3278</v>
       </c>
       <c r="D5" t="n">
-        <v>1286</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="C6" t="n">
-        <v>1524</v>
+        <v>1152</v>
       </c>
       <c r="D6" t="n">
-        <v>929</v>
+        <v>945</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
         <v>664</v>
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7025</v>
+        <v>5473</v>
       </c>
       <c r="C2" t="n">
-        <v>8813</v>
+        <v>12492</v>
       </c>
       <c r="D2" t="n">
-        <v>49181</v>
+        <v>18764</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3509</v>
+        <v>3337</v>
       </c>
       <c r="C3" t="n">
-        <v>5631</v>
+        <v>7460</v>
       </c>
       <c r="D3" t="n">
-        <v>13252</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1991</v>
+        <v>1922</v>
       </c>
       <c r="C4" t="n">
-        <v>5189</v>
+        <v>4664</v>
       </c>
       <c r="D4" t="n">
-        <v>3295</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>958</v>
+        <v>921</v>
       </c>
       <c r="C5" t="n">
-        <v>3976</v>
+        <v>2995</v>
       </c>
       <c r="D5" t="n">
-        <v>1182</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="C6" t="n">
-        <v>2045</v>
+        <v>1475</v>
       </c>
       <c r="D6" t="n">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>574</v>
+        <v>475</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5986,7 +5986,7 @@
         <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5894</v>
+        <v>5036</v>
       </c>
       <c r="C2" t="n">
-        <v>8495</v>
+        <v>6194</v>
       </c>
       <c r="D2" t="n">
-        <v>47096</v>
+        <v>16890</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4304</v>
+        <v>3641</v>
       </c>
       <c r="C3" t="n">
-        <v>6392</v>
+        <v>8945</v>
       </c>
       <c r="D3" t="n">
-        <v>18046</v>
+        <v>7983</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2376</v>
+        <v>2280</v>
       </c>
       <c r="C4" t="n">
-        <v>5335</v>
+        <v>6258</v>
       </c>
       <c r="D4" t="n">
-        <v>5074</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1283</v>
+        <v>1269</v>
       </c>
       <c r="C5" t="n">
-        <v>4568</v>
+        <v>3910</v>
       </c>
       <c r="D5" t="n">
-        <v>1551</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="C6" t="n">
-        <v>3039</v>
+        <v>2317</v>
       </c>
       <c r="D6" t="n">
-        <v>818</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C7" t="n">
-        <v>1366</v>
+        <v>1033</v>
       </c>
       <c r="D7" t="n">
-        <v>542</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>403</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6266,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4601</v>
+        <v>4959</v>
       </c>
       <c r="C2" t="n">
-        <v>7347</v>
+        <v>8907</v>
       </c>
       <c r="D2" t="n">
-        <v>36396</v>
+        <v>24463</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4149</v>
+        <v>3587</v>
       </c>
       <c r="C3" t="n">
-        <v>6499</v>
+        <v>6480</v>
       </c>
       <c r="D3" t="n">
-        <v>21191</v>
+        <v>8833</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2820</v>
+        <v>2518</v>
       </c>
       <c r="C4" t="n">
-        <v>5782</v>
+        <v>7623</v>
       </c>
       <c r="D4" t="n">
-        <v>7285</v>
+        <v>3783</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1566</v>
+        <v>1557</v>
       </c>
       <c r="C5" t="n">
-        <v>4819</v>
+        <v>5053</v>
       </c>
       <c r="D5" t="n">
-        <v>2112</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C6" t="n">
-        <v>3769</v>
+        <v>3131</v>
       </c>
       <c r="D6" t="n">
-        <v>918</v>
+        <v>857</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C7" t="n">
-        <v>2185</v>
+        <v>1699</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>851</v>
+        <v>690</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6636,7 +6636,7 @@
         <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_67_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_67_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6069</v>
+        <v>4741</v>
       </c>
       <c r="C2" t="n">
-        <v>14703</v>
+        <v>9995</v>
       </c>
       <c r="D2" t="n">
-        <v>24382</v>
+        <v>25330</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3456</v>
+        <v>3124</v>
       </c>
       <c r="C3" t="n">
-        <v>6700</v>
+        <v>7281</v>
       </c>
       <c r="D3" t="n">
-        <v>10476</v>
+        <v>16931</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2567</v>
+        <v>2414</v>
       </c>
       <c r="C4" t="n">
-        <v>6809</v>
+        <v>6366</v>
       </c>
       <c r="D4" t="n">
-        <v>4540</v>
+        <v>7493</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1756</v>
+        <v>1558</v>
       </c>
       <c r="C5" t="n">
-        <v>6230</v>
+        <v>5458</v>
       </c>
       <c r="D5" t="n">
-        <v>1790</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1060</v>
+        <v>841</v>
       </c>
       <c r="C6" t="n">
-        <v>4020</v>
+        <v>4108</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>491</v>
+        <v>386</v>
       </c>
       <c r="C7" t="n">
-        <v>2355</v>
+        <v>2732</v>
       </c>
       <c r="D7" t="n">
-        <v>615</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="C8" t="n">
-        <v>1154</v>
+        <v>1321</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>457</v>
+        <v>511</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7003</v>
+        <v>6258</v>
       </c>
       <c r="C2" t="n">
-        <v>13298</v>
+        <v>14714</v>
       </c>
       <c r="D2" t="n">
-        <v>31047</v>
+        <v>22740</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3708</v>
+        <v>3102</v>
       </c>
       <c r="C3" t="n">
-        <v>8990</v>
+        <v>7462</v>
       </c>
       <c r="D3" t="n">
-        <v>11568</v>
+        <v>16895</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2511</v>
+        <v>2313</v>
       </c>
       <c r="C4" t="n">
-        <v>6551</v>
+        <v>6646</v>
       </c>
       <c r="D4" t="n">
-        <v>5270</v>
+        <v>8714</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1858</v>
+        <v>1702</v>
       </c>
       <c r="C5" t="n">
-        <v>6361</v>
+        <v>5684</v>
       </c>
       <c r="D5" t="n">
-        <v>2157</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1243</v>
+        <v>1023</v>
       </c>
       <c r="C6" t="n">
-        <v>4897</v>
+        <v>4600</v>
       </c>
       <c r="D6" t="n">
-        <v>1044</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>647</v>
+        <v>507</v>
       </c>
       <c r="C7" t="n">
-        <v>3072</v>
+        <v>3310</v>
       </c>
       <c r="D7" t="n">
-        <v>657</v>
+        <v>697</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>270</v>
+        <v>212</v>
       </c>
       <c r="C8" t="n">
-        <v>1636</v>
+        <v>1874</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C9" t="n">
-        <v>732</v>
+        <v>828</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8556</v>
+        <v>6036</v>
       </c>
       <c r="C2" t="n">
-        <v>14415</v>
+        <v>13729</v>
       </c>
       <c r="D2" t="n">
-        <v>35367</v>
+        <v>24770</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4038</v>
+        <v>3470</v>
       </c>
       <c r="C3" t="n">
-        <v>9600</v>
+        <v>9098</v>
       </c>
       <c r="D3" t="n">
-        <v>13165</v>
+        <v>16495</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2527</v>
+        <v>2225</v>
       </c>
       <c r="C4" t="n">
-        <v>7358</v>
+        <v>6772</v>
       </c>
       <c r="D4" t="n">
-        <v>6016</v>
+        <v>9464</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1881</v>
+        <v>1723</v>
       </c>
       <c r="C5" t="n">
-        <v>6244</v>
+        <v>5889</v>
       </c>
       <c r="D5" t="n">
-        <v>2489</v>
+        <v>3889</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1353</v>
+        <v>1161</v>
       </c>
       <c r="C6" t="n">
-        <v>5383</v>
+        <v>4977</v>
       </c>
       <c r="D6" t="n">
-        <v>1180</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>785</v>
+        <v>625</v>
       </c>
       <c r="C7" t="n">
-        <v>3786</v>
+        <v>3756</v>
       </c>
       <c r="D7" t="n">
-        <v>693</v>
+        <v>764</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>365</v>
+        <v>282</v>
       </c>
       <c r="C8" t="n">
-        <v>2154</v>
+        <v>2375</v>
       </c>
       <c r="D8" t="n">
-        <v>463</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="C9" t="n">
-        <v>1052</v>
+        <v>1188</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C10" t="n">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
         <v>228</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7816</v>
+        <v>5662</v>
       </c>
       <c r="C2" t="n">
-        <v>10148</v>
+        <v>9665</v>
       </c>
       <c r="D2" t="n">
-        <v>28925</v>
+        <v>20766</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4630</v>
+        <v>4024</v>
       </c>
       <c r="C3" t="n">
-        <v>13778</v>
+        <v>13042</v>
       </c>
       <c r="D3" t="n">
-        <v>13854</v>
+        <v>17883</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1738</v>
+        <v>1592</v>
       </c>
       <c r="C4" t="n">
-        <v>9879</v>
+        <v>9164</v>
       </c>
       <c r="D4" t="n">
-        <v>5647</v>
+        <v>8812</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1250</v>
+        <v>1072</v>
       </c>
       <c r="C5" t="n">
-        <v>5275</v>
+        <v>4877</v>
       </c>
       <c r="D5" t="n">
-        <v>1825</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>725</v>
+        <v>577</v>
       </c>
       <c r="C6" t="n">
-        <v>3710</v>
+        <v>3680</v>
       </c>
       <c r="D6" t="n">
-        <v>679</v>
+        <v>748</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>337</v>
+        <v>260</v>
       </c>
       <c r="C7" t="n">
-        <v>2110</v>
+        <v>2327</v>
       </c>
       <c r="D7" t="n">
-        <v>453</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>1030</v>
+        <v>1164</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
         <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
         <v>37</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4625</v>
+        <v>3528</v>
       </c>
       <c r="C2" t="n">
-        <v>5072</v>
+        <v>4849</v>
       </c>
       <c r="D2" t="n">
-        <v>21495</v>
+        <v>14536</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5081</v>
+        <v>4052</v>
       </c>
       <c r="C3" t="n">
-        <v>11069</v>
+        <v>10549</v>
       </c>
       <c r="D3" t="n">
-        <v>15007</v>
+        <v>17250</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2427</v>
+        <v>2141</v>
       </c>
       <c r="C4" t="n">
-        <v>11812</v>
+        <v>11037</v>
       </c>
       <c r="D4" t="n">
-        <v>6765</v>
+        <v>10019</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1371</v>
+        <v>1193</v>
       </c>
       <c r="C5" t="n">
-        <v>7230</v>
+        <v>6655</v>
       </c>
       <c r="D5" t="n">
-        <v>2244</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>848</v>
+        <v>673</v>
       </c>
       <c r="C6" t="n">
-        <v>4412</v>
+        <v>4249</v>
       </c>
       <c r="D6" t="n">
-        <v>789</v>
+        <v>917</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="C7" t="n">
-        <v>2702</v>
+        <v>2839</v>
       </c>
       <c r="D7" t="n">
-        <v>489</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C8" t="n">
-        <v>1339</v>
+        <v>1519</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3954</v>
+        <v>3191</v>
       </c>
       <c r="C2" t="n">
-        <v>6964</v>
+        <v>11553</v>
       </c>
       <c r="D2" t="n">
-        <v>19865</v>
+        <v>13658</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4114</v>
+        <v>3234</v>
       </c>
       <c r="C3" t="n">
-        <v>7448</v>
+        <v>7166</v>
       </c>
       <c r="D3" t="n">
-        <v>15024</v>
+        <v>15887</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3034</v>
+        <v>2513</v>
       </c>
       <c r="C4" t="n">
-        <v>11216</v>
+        <v>10582</v>
       </c>
       <c r="D4" t="n">
-        <v>7760</v>
+        <v>10825</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1601</v>
+        <v>1384</v>
       </c>
       <c r="C5" t="n">
-        <v>9147</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="n">
-        <v>2870</v>
+        <v>4093</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>971</v>
+        <v>810</v>
       </c>
       <c r="C6" t="n">
-        <v>5631</v>
+        <v>5267</v>
       </c>
       <c r="D6" t="n">
-        <v>988</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>453</v>
+        <v>350</v>
       </c>
       <c r="C7" t="n">
-        <v>3431</v>
+        <v>3404</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>1872</v>
+        <v>2037</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>793</v>
+        <v>870</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>35</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2579,7 +2579,7 @@
         <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2403</v>
+        <v>1953</v>
       </c>
       <c r="C2" t="n">
-        <v>3428</v>
+        <v>5668</v>
       </c>
       <c r="D2" t="n">
-        <v>14009</v>
+        <v>9646</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3973</v>
+        <v>3116</v>
       </c>
       <c r="C3" t="n">
-        <v>7034</v>
+        <v>8351</v>
       </c>
       <c r="D3" t="n">
-        <v>15176</v>
+        <v>15342</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3295</v>
+        <v>2738</v>
       </c>
       <c r="C4" t="n">
-        <v>11009</v>
+        <v>10361</v>
       </c>
       <c r="D4" t="n">
-        <v>8509</v>
+        <v>11482</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1674</v>
+        <v>1418</v>
       </c>
       <c r="C5" t="n">
-        <v>11004</v>
+        <v>10212</v>
       </c>
       <c r="D5" t="n">
-        <v>2965</v>
+        <v>4204</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>795</v>
+        <v>637</v>
       </c>
       <c r="C6" t="n">
-        <v>6517</v>
+        <v>6159</v>
       </c>
       <c r="D6" t="n">
-        <v>980</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>3488</v>
+        <v>3585</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n">
-        <v>1309</v>
+        <v>1431</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
         <v>34</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2876,7 +2876,7 @@
         <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2644</v>
+        <v>2368</v>
       </c>
       <c r="C2" t="n">
-        <v>5955</v>
+        <v>7912</v>
       </c>
       <c r="D2" t="n">
-        <v>15532</v>
+        <v>9416</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2882</v>
+        <v>2281</v>
       </c>
       <c r="C3" t="n">
-        <v>4895</v>
+        <v>6460</v>
       </c>
       <c r="D3" t="n">
-        <v>14031</v>
+        <v>13606</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3105</v>
+        <v>2545</v>
       </c>
       <c r="C4" t="n">
-        <v>9092</v>
+        <v>9257</v>
       </c>
       <c r="D4" t="n">
-        <v>9274</v>
+        <v>11836</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2037</v>
+        <v>1700</v>
       </c>
       <c r="C5" t="n">
-        <v>10777</v>
+        <v>10160</v>
       </c>
       <c r="D5" t="n">
-        <v>3701</v>
+        <v>5054</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1014</v>
+        <v>821</v>
       </c>
       <c r="C6" t="n">
-        <v>8396</v>
+        <v>7761</v>
       </c>
       <c r="D6" t="n">
-        <v>1215</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>287</v>
+        <v>231</v>
       </c>
       <c r="C7" t="n">
-        <v>4648</v>
+        <v>4612</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>2081</v>
+        <v>2176</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>624</v>
+        <v>653</v>
       </c>
       <c r="D9" t="n">
         <v>289</v>
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
         <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>43</v>
+      </c>
+      <c r="D14" t="n">
         <v>45</v>
-      </c>
-      <c r="D14" t="n">
-        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>32</v>
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1811</v>
+        <v>1548</v>
       </c>
       <c r="C2" t="n">
-        <v>5056</v>
+        <v>4698</v>
       </c>
       <c r="D2" t="n">
-        <v>12359</v>
+        <v>8380</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2465</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="n">
-        <v>4867</v>
+        <v>6441</v>
       </c>
       <c r="D3" t="n">
-        <v>13458</v>
+        <v>12418</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2803</v>
+        <v>2278</v>
       </c>
       <c r="C4" t="n">
-        <v>7506</v>
+        <v>8194</v>
       </c>
       <c r="D4" t="n">
-        <v>9674</v>
+        <v>11810</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2204</v>
+        <v>1847</v>
       </c>
       <c r="C5" t="n">
-        <v>10400</v>
+        <v>10035</v>
       </c>
       <c r="D5" t="n">
-        <v>4248</v>
+        <v>5713</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1170</v>
+        <v>937</v>
       </c>
       <c r="C6" t="n">
-        <v>9418</v>
+        <v>8761</v>
       </c>
       <c r="D6" t="n">
-        <v>1415</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="C7" t="n">
-        <v>5773</v>
+        <v>5605</v>
       </c>
       <c r="D7" t="n">
-        <v>643</v>
+        <v>712</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
-        <v>2633</v>
+        <v>2722</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>661</v>
+        <v>690</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
         <v>91</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D14" t="n">
         <v>35</v>
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2644</v>
+        <v>2005</v>
       </c>
       <c r="C2" t="n">
-        <v>5015</v>
+        <v>12157</v>
       </c>
       <c r="D2" t="n">
-        <v>16332</v>
+        <v>11132</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1899</v>
+        <v>1576</v>
       </c>
       <c r="C3" t="n">
-        <v>4455</v>
+        <v>5189</v>
       </c>
       <c r="D3" t="n">
-        <v>12495</v>
+        <v>11190</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2340</v>
+        <v>1908</v>
       </c>
       <c r="C4" t="n">
-        <v>6311</v>
+        <v>7333</v>
       </c>
       <c r="D4" t="n">
-        <v>9888</v>
+        <v>11532</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2186</v>
+        <v>1813</v>
       </c>
       <c r="C5" t="n">
-        <v>9000</v>
+        <v>9137</v>
       </c>
       <c r="D5" t="n">
-        <v>4796</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1390</v>
+        <v>1135</v>
       </c>
       <c r="C6" t="n">
-        <v>9793</v>
+        <v>9145</v>
       </c>
       <c r="D6" t="n">
-        <v>1709</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>462</v>
+        <v>371</v>
       </c>
       <c r="C7" t="n">
-        <v>7020</v>
+        <v>6685</v>
       </c>
       <c r="D7" t="n">
-        <v>727</v>
+        <v>838</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>3647</v>
+        <v>3679</v>
       </c>
       <c r="D8" t="n">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>1266</v>
+        <v>1287</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="D10" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>35</v>
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5969</v>
+        <v>4979</v>
       </c>
       <c r="C2" t="n">
-        <v>11770</v>
+        <v>14607</v>
       </c>
       <c r="D2" t="n">
-        <v>4156</v>
+        <v>12668</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1954</v>
+        <v>1480</v>
       </c>
       <c r="C2" t="n">
-        <v>2969</v>
+        <v>7294</v>
       </c>
       <c r="D2" t="n">
-        <v>12151</v>
+        <v>8282</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2584</v>
+        <v>2121</v>
       </c>
       <c r="C3" t="n">
-        <v>5098</v>
+        <v>7204</v>
       </c>
       <c r="D3" t="n">
-        <v>13669</v>
+        <v>12251</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3216</v>
+        <v>2650</v>
       </c>
       <c r="C4" t="n">
-        <v>9303</v>
+        <v>10405</v>
       </c>
       <c r="D4" t="n">
-        <v>9930</v>
+        <v>11757</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1284</v>
+        <v>1048</v>
       </c>
       <c r="C5" t="n">
-        <v>13581</v>
+        <v>13052</v>
       </c>
       <c r="D5" t="n">
-        <v>4261</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>426</v>
+        <v>342</v>
       </c>
       <c r="C6" t="n">
-        <v>8511</v>
+        <v>8074</v>
       </c>
       <c r="D6" t="n">
-        <v>1447</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>3574</v>
+        <v>3605</v>
       </c>
       <c r="D7" t="n">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1240</v>
+        <v>1261</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D12" t="n">
         <v>60</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
         <v>34</v>
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6849</v>
+        <v>5706</v>
       </c>
       <c r="C2" t="n">
-        <v>6589</v>
+        <v>9233</v>
       </c>
       <c r="D2" t="n">
-        <v>6061</v>
+        <v>14664</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2536</v>
+        <v>2116</v>
       </c>
       <c r="C3" t="n">
-        <v>5932</v>
+        <v>7361</v>
       </c>
       <c r="D3" t="n">
-        <v>1337</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5492</v>
+        <v>3753</v>
       </c>
       <c r="C2" t="n">
-        <v>6794</v>
+        <v>6484</v>
       </c>
       <c r="D2" t="n">
-        <v>13619</v>
+        <v>18982</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3853</v>
+        <v>3211</v>
       </c>
       <c r="C3" t="n">
-        <v>5436</v>
+        <v>7261</v>
       </c>
       <c r="D3" t="n">
-        <v>2032</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1135</v>
+        <v>953</v>
       </c>
       <c r="C4" t="n">
-        <v>3517</v>
+        <v>4356</v>
       </c>
       <c r="D4" t="n">
-        <v>1450</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5151</v>
+        <v>4692</v>
       </c>
       <c r="C2" t="n">
-        <v>9162</v>
+        <v>10179</v>
       </c>
       <c r="D2" t="n">
-        <v>15434</v>
+        <v>21306</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3827</v>
+        <v>2863</v>
       </c>
       <c r="C3" t="n">
-        <v>5346</v>
+        <v>5936</v>
       </c>
       <c r="D3" t="n">
-        <v>3739</v>
+        <v>6540</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2121</v>
+        <v>1743</v>
       </c>
       <c r="C4" t="n">
-        <v>4530</v>
+        <v>5882</v>
       </c>
       <c r="D4" t="n">
-        <v>1517</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>516</v>
+        <v>445</v>
       </c>
       <c r="C5" t="n">
-        <v>2019</v>
+        <v>2438</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>631</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5534</v>
+        <v>5880</v>
       </c>
       <c r="C2" t="n">
-        <v>11733</v>
+        <v>7044</v>
       </c>
       <c r="D2" t="n">
-        <v>17678</v>
+        <v>30346</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3697</v>
+        <v>3043</v>
       </c>
       <c r="C3" t="n">
-        <v>6362</v>
+        <v>7043</v>
       </c>
       <c r="D3" t="n">
-        <v>5253</v>
+        <v>8324</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2493</v>
+        <v>1953</v>
       </c>
       <c r="C4" t="n">
-        <v>4874</v>
+        <v>5788</v>
       </c>
       <c r="D4" t="n">
-        <v>1876</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1080</v>
+        <v>887</v>
       </c>
       <c r="C5" t="n">
-        <v>3278</v>
+        <v>4116</v>
       </c>
       <c r="D5" t="n">
-        <v>1195</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>289</v>
+        <v>256</v>
       </c>
       <c r="C6" t="n">
-        <v>1152</v>
+        <v>1367</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>935</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
         <v>664</v>
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,7 +5557,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
         <v>234</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5473</v>
+        <v>5556</v>
       </c>
       <c r="C2" t="n">
-        <v>12492</v>
+        <v>10652</v>
       </c>
       <c r="D2" t="n">
-        <v>18764</v>
+        <v>36507</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3337</v>
+        <v>3179</v>
       </c>
       <c r="C3" t="n">
-        <v>7460</v>
+        <v>5779</v>
       </c>
       <c r="D3" t="n">
-        <v>6370</v>
+        <v>10261</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1922</v>
+        <v>1540</v>
       </c>
       <c r="C4" t="n">
-        <v>4664</v>
+        <v>5231</v>
       </c>
       <c r="D4" t="n">
-        <v>2124</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>921</v>
+        <v>728</v>
       </c>
       <c r="C5" t="n">
-        <v>2995</v>
+        <v>3619</v>
       </c>
       <c r="D5" t="n">
-        <v>1024</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>321</v>
+        <v>265</v>
       </c>
       <c r="C6" t="n">
-        <v>1475</v>
+        <v>1807</v>
       </c>
       <c r="D6" t="n">
-        <v>751</v>
+        <v>759</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>475</v>
+        <v>536</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>92</v>
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5036</v>
+        <v>4461</v>
       </c>
       <c r="C2" t="n">
-        <v>6194</v>
+        <v>8282</v>
       </c>
       <c r="D2" t="n">
-        <v>16890</v>
+        <v>34916</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3641</v>
+        <v>3594</v>
       </c>
       <c r="C3" t="n">
-        <v>8945</v>
+        <v>7361</v>
       </c>
       <c r="D3" t="n">
-        <v>7983</v>
+        <v>13915</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2280</v>
+        <v>2050</v>
       </c>
       <c r="C4" t="n">
-        <v>6258</v>
+        <v>5443</v>
       </c>
       <c r="D4" t="n">
-        <v>2895</v>
+        <v>4582</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1269</v>
+        <v>992</v>
       </c>
       <c r="C5" t="n">
-        <v>3910</v>
+        <v>4422</v>
       </c>
       <c r="D5" t="n">
-        <v>1214</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>571</v>
+        <v>455</v>
       </c>
       <c r="C6" t="n">
-        <v>2317</v>
+        <v>2794</v>
       </c>
       <c r="D6" t="n">
-        <v>792</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="C7" t="n">
-        <v>1033</v>
+        <v>1233</v>
       </c>
       <c r="D7" t="n">
-        <v>548</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6207,7 +6207,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>102</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4959</v>
+        <v>4423</v>
       </c>
       <c r="C2" t="n">
-        <v>8907</v>
+        <v>9985</v>
       </c>
       <c r="D2" t="n">
-        <v>24463</v>
+        <v>30012</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3587</v>
+        <v>3300</v>
       </c>
       <c r="C3" t="n">
-        <v>6480</v>
+        <v>6819</v>
       </c>
       <c r="D3" t="n">
-        <v>8833</v>
+        <v>16127</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2518</v>
+        <v>2399</v>
       </c>
       <c r="C4" t="n">
-        <v>7623</v>
+        <v>6308</v>
       </c>
       <c r="D4" t="n">
-        <v>3783</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1557</v>
+        <v>1299</v>
       </c>
       <c r="C5" t="n">
-        <v>5053</v>
+        <v>4869</v>
       </c>
       <c r="D5" t="n">
-        <v>1472</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>823</v>
+        <v>642</v>
       </c>
       <c r="C6" t="n">
-        <v>3131</v>
+        <v>3591</v>
       </c>
       <c r="D6" t="n">
-        <v>857</v>
+        <v>968</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333</v>
+        <v>266</v>
       </c>
       <c r="C7" t="n">
-        <v>1699</v>
+        <v>2000</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>690</v>
+        <v>801</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>28</v>
@@ -6650,7 +6650,7 @@
         <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_67_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_67_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4741</v>
+        <v>940</v>
       </c>
       <c r="C2" t="n">
-        <v>9995</v>
+        <v>2974</v>
       </c>
       <c r="D2" t="n">
-        <v>25330</v>
+        <v>15157</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3124</v>
+        <v>1234</v>
       </c>
       <c r="C3" t="n">
-        <v>7281</v>
+        <v>6953</v>
       </c>
       <c r="D3" t="n">
-        <v>16931</v>
+        <v>16266</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2414</v>
+        <v>811</v>
       </c>
       <c r="C4" t="n">
-        <v>6366</v>
+        <v>7357</v>
       </c>
       <c r="D4" t="n">
-        <v>7493</v>
+        <v>7437</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1558</v>
+        <v>467</v>
       </c>
       <c r="C5" t="n">
-        <v>5458</v>
+        <v>4366</v>
       </c>
       <c r="D5" t="n">
-        <v>2713</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>841</v>
+        <v>213</v>
       </c>
       <c r="C6" t="n">
-        <v>4108</v>
+        <v>1784</v>
       </c>
       <c r="D6" t="n">
-        <v>1124</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>386</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>2732</v>
+        <v>675</v>
       </c>
       <c r="D7" t="n">
-        <v>645</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>147</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1321</v>
+        <v>346</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>511</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6258</v>
+        <v>750</v>
       </c>
       <c r="C2" t="n">
-        <v>14714</v>
+        <v>3333</v>
       </c>
       <c r="D2" t="n">
-        <v>22740</v>
+        <v>23770</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3102</v>
+        <v>928</v>
       </c>
       <c r="C3" t="n">
-        <v>7462</v>
+        <v>4250</v>
       </c>
       <c r="D3" t="n">
-        <v>16895</v>
+        <v>15073</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2313</v>
+        <v>870</v>
       </c>
       <c r="C4" t="n">
-        <v>6646</v>
+        <v>6982</v>
       </c>
       <c r="D4" t="n">
-        <v>8714</v>
+        <v>8821</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1702</v>
+        <v>562</v>
       </c>
       <c r="C5" t="n">
-        <v>5684</v>
+        <v>5896</v>
       </c>
       <c r="D5" t="n">
-        <v>3292</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1023</v>
+        <v>296</v>
       </c>
       <c r="C6" t="n">
-        <v>4600</v>
+        <v>3071</v>
       </c>
       <c r="D6" t="n">
-        <v>1337</v>
+        <v>992</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>507</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>3310</v>
+        <v>1213</v>
       </c>
       <c r="D7" t="n">
-        <v>697</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1874</v>
+        <v>497</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>828</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>330</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6036</v>
+        <v>395</v>
       </c>
       <c r="C2" t="n">
-        <v>13729</v>
+        <v>1408</v>
       </c>
       <c r="D2" t="n">
-        <v>24770</v>
+        <v>15996</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3470</v>
+        <v>844</v>
       </c>
       <c r="C3" t="n">
-        <v>9098</v>
+        <v>3713</v>
       </c>
       <c r="D3" t="n">
-        <v>16495</v>
+        <v>15776</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2225</v>
+        <v>969</v>
       </c>
       <c r="C4" t="n">
-        <v>6772</v>
+        <v>6498</v>
       </c>
       <c r="D4" t="n">
-        <v>9464</v>
+        <v>9781</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1723</v>
+        <v>580</v>
       </c>
       <c r="C5" t="n">
-        <v>5889</v>
+        <v>6857</v>
       </c>
       <c r="D5" t="n">
-        <v>3889</v>
+        <v>3477</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1161</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>4977</v>
+        <v>4009</v>
       </c>
       <c r="D6" t="n">
-        <v>1582</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>625</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3756</v>
+        <v>1179</v>
       </c>
       <c r="D7" t="n">
-        <v>764</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>282</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2375</v>
+        <v>486</v>
       </c>
       <c r="D8" t="n">
-        <v>473</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1188</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>228</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5662</v>
+        <v>356</v>
       </c>
       <c r="C2" t="n">
-        <v>9665</v>
+        <v>6786</v>
       </c>
       <c r="D2" t="n">
-        <v>20766</v>
+        <v>14122</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4024</v>
+        <v>548</v>
       </c>
       <c r="C3" t="n">
-        <v>13042</v>
+        <v>2234</v>
       </c>
       <c r="D3" t="n">
-        <v>17883</v>
+        <v>14850</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1592</v>
+        <v>811</v>
       </c>
       <c r="C4" t="n">
-        <v>9164</v>
+        <v>4954</v>
       </c>
       <c r="D4" t="n">
-        <v>8812</v>
+        <v>10519</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1072</v>
+        <v>673</v>
       </c>
       <c r="C5" t="n">
-        <v>4877</v>
+        <v>6600</v>
       </c>
       <c r="D5" t="n">
-        <v>2558</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>577</v>
+        <v>355</v>
       </c>
       <c r="C6" t="n">
-        <v>3680</v>
+        <v>5386</v>
       </c>
       <c r="D6" t="n">
-        <v>748</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>260</v>
+        <v>122</v>
       </c>
       <c r="C7" t="n">
-        <v>2327</v>
+        <v>2449</v>
       </c>
       <c r="D7" t="n">
-        <v>463</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1164</v>
+        <v>773</v>
       </c>
       <c r="D8" t="n">
-        <v>314</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>490</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>67</v>
+      </c>
+      <c r="D15" t="n">
         <v>49</v>
-      </c>
-      <c r="D15" t="n">
-        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3528</v>
+        <v>217</v>
       </c>
       <c r="C2" t="n">
-        <v>4849</v>
+        <v>3514</v>
       </c>
       <c r="D2" t="n">
-        <v>14536</v>
+        <v>10551</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4052</v>
+        <v>417</v>
       </c>
       <c r="C3" t="n">
-        <v>10549</v>
+        <v>3862</v>
       </c>
       <c r="D3" t="n">
-        <v>17250</v>
+        <v>13895</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2141</v>
+        <v>660</v>
       </c>
       <c r="C4" t="n">
-        <v>11037</v>
+        <v>3714</v>
       </c>
       <c r="D4" t="n">
-        <v>10019</v>
+        <v>10965</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1193</v>
+        <v>703</v>
       </c>
       <c r="C5" t="n">
-        <v>6655</v>
+        <v>6020</v>
       </c>
       <c r="D5" t="n">
-        <v>3249</v>
+        <v>5173</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>673</v>
+        <v>428</v>
       </c>
       <c r="C6" t="n">
-        <v>4249</v>
+        <v>6102</v>
       </c>
       <c r="D6" t="n">
-        <v>917</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>243</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>2839</v>
+        <v>3479</v>
       </c>
       <c r="D7" t="n">
-        <v>505</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1519</v>
+        <v>1193</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>509</v>
+        <v>433</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3191</v>
+        <v>397</v>
       </c>
       <c r="C2" t="n">
-        <v>11553</v>
+        <v>5686</v>
       </c>
       <c r="D2" t="n">
-        <v>13658</v>
+        <v>12698</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3234</v>
+        <v>282</v>
       </c>
       <c r="C3" t="n">
-        <v>7166</v>
+        <v>3250</v>
       </c>
       <c r="D3" t="n">
-        <v>15887</v>
+        <v>12506</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2513</v>
+        <v>488</v>
       </c>
       <c r="C4" t="n">
-        <v>10582</v>
+        <v>3744</v>
       </c>
       <c r="D4" t="n">
-        <v>10825</v>
+        <v>11109</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1384</v>
+        <v>635</v>
       </c>
       <c r="C5" t="n">
-        <v>8451</v>
+        <v>4832</v>
       </c>
       <c r="D5" t="n">
-        <v>4093</v>
+        <v>5905</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>810</v>
+        <v>498</v>
       </c>
       <c r="C6" t="n">
-        <v>5267</v>
+        <v>6007</v>
       </c>
       <c r="D6" t="n">
-        <v>1240</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>350</v>
+        <v>219</v>
       </c>
       <c r="C7" t="n">
-        <v>3404</v>
+        <v>4642</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>816</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>2037</v>
+        <v>2122</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>870</v>
+        <v>720</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>328</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1953</v>
+        <v>266</v>
       </c>
       <c r="C2" t="n">
-        <v>5668</v>
+        <v>2956</v>
       </c>
       <c r="D2" t="n">
-        <v>9646</v>
+        <v>9142</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3116</v>
+        <v>424</v>
       </c>
       <c r="C3" t="n">
-        <v>8351</v>
+        <v>4181</v>
       </c>
       <c r="D3" t="n">
-        <v>15342</v>
+        <v>13554</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2738</v>
+        <v>822</v>
       </c>
       <c r="C4" t="n">
-        <v>10361</v>
+        <v>5377</v>
       </c>
       <c r="D4" t="n">
-        <v>11482</v>
+        <v>11435</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1418</v>
+        <v>507</v>
       </c>
       <c r="C5" t="n">
-        <v>10212</v>
+        <v>7801</v>
       </c>
       <c r="D5" t="n">
-        <v>4204</v>
+        <v>5397</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>637</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>6159</v>
+        <v>6020</v>
       </c>
       <c r="D6" t="n">
-        <v>1212</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C7" t="n">
-        <v>3585</v>
+        <v>2079</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1431</v>
+        <v>705</v>
       </c>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2368</v>
+        <v>203</v>
       </c>
       <c r="C2" t="n">
-        <v>7912</v>
+        <v>2285</v>
       </c>
       <c r="D2" t="n">
-        <v>9416</v>
+        <v>7047</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2281</v>
+        <v>301</v>
       </c>
       <c r="C3" t="n">
-        <v>6460</v>
+        <v>3153</v>
       </c>
       <c r="D3" t="n">
-        <v>13606</v>
+        <v>11947</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2545</v>
+        <v>536</v>
       </c>
       <c r="C4" t="n">
-        <v>9257</v>
+        <v>4521</v>
       </c>
       <c r="D4" t="n">
-        <v>11836</v>
+        <v>10983</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1700</v>
+        <v>461</v>
       </c>
       <c r="C5" t="n">
-        <v>10160</v>
+        <v>5851</v>
       </c>
       <c r="D5" t="n">
-        <v>5054</v>
+        <v>5644</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>821</v>
+        <v>192</v>
       </c>
       <c r="C6" t="n">
-        <v>7761</v>
+        <v>5644</v>
       </c>
       <c r="D6" t="n">
-        <v>1569</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>231</v>
+        <v>53</v>
       </c>
       <c r="C7" t="n">
-        <v>4612</v>
+        <v>2713</v>
       </c>
       <c r="D7" t="n">
-        <v>633</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>2176</v>
+        <v>805</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>653</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>131</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1548</v>
+        <v>320</v>
       </c>
       <c r="C2" t="n">
-        <v>4698</v>
+        <v>9614</v>
       </c>
       <c r="D2" t="n">
-        <v>8380</v>
+        <v>11727</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
+        <v>212</v>
       </c>
       <c r="C3" t="n">
-        <v>6441</v>
+        <v>2319</v>
       </c>
       <c r="D3" t="n">
-        <v>12418</v>
+        <v>10302</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2278</v>
+        <v>374</v>
       </c>
       <c r="C4" t="n">
-        <v>8194</v>
+        <v>3695</v>
       </c>
       <c r="D4" t="n">
-        <v>11810</v>
+        <v>10834</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1847</v>
+        <v>448</v>
       </c>
       <c r="C5" t="n">
-        <v>10035</v>
+        <v>5014</v>
       </c>
       <c r="D5" t="n">
-        <v>5713</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>937</v>
+        <v>289</v>
       </c>
       <c r="C6" t="n">
-        <v>8761</v>
+        <v>5743</v>
       </c>
       <c r="D6" t="n">
-        <v>1848</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>206</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>5605</v>
+        <v>4203</v>
       </c>
       <c r="D7" t="n">
-        <v>712</v>
+        <v>820</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>2722</v>
+        <v>1710</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>690</v>
+        <v>511</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2005</v>
+        <v>639</v>
       </c>
       <c r="C2" t="n">
-        <v>12157</v>
+        <v>8767</v>
       </c>
       <c r="D2" t="n">
-        <v>11132</v>
+        <v>11923</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1576</v>
+        <v>214</v>
       </c>
       <c r="C3" t="n">
-        <v>5189</v>
+        <v>5177</v>
       </c>
       <c r="D3" t="n">
-        <v>11190</v>
+        <v>9798</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1908</v>
+        <v>262</v>
       </c>
       <c r="C4" t="n">
-        <v>7333</v>
+        <v>2904</v>
       </c>
       <c r="D4" t="n">
-        <v>11532</v>
+        <v>10308</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1813</v>
+        <v>381</v>
       </c>
       <c r="C5" t="n">
-        <v>9137</v>
+        <v>4251</v>
       </c>
       <c r="D5" t="n">
-        <v>6300</v>
+        <v>7008</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1135</v>
+        <v>332</v>
       </c>
       <c r="C6" t="n">
-        <v>9145</v>
+        <v>5333</v>
       </c>
       <c r="D6" t="n">
-        <v>2251</v>
+        <v>3148</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>371</v>
+        <v>163</v>
       </c>
       <c r="C7" t="n">
-        <v>6685</v>
+        <v>4925</v>
       </c>
       <c r="D7" t="n">
-        <v>838</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>3679</v>
+        <v>2833</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1287</v>
+        <v>1027</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>353</v>
+        <v>322</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4979</v>
+        <v>2535</v>
       </c>
       <c r="C2" t="n">
-        <v>14607</v>
+        <v>8710</v>
       </c>
       <c r="D2" t="n">
-        <v>12668</v>
+        <v>17194</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1480</v>
+        <v>601</v>
       </c>
       <c r="C2" t="n">
-        <v>7294</v>
+        <v>15907</v>
       </c>
       <c r="D2" t="n">
-        <v>8282</v>
+        <v>17244</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2121</v>
+        <v>317</v>
       </c>
       <c r="C3" t="n">
-        <v>7204</v>
+        <v>5971</v>
       </c>
       <c r="D3" t="n">
-        <v>12251</v>
+        <v>9428</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2650</v>
+        <v>210</v>
       </c>
       <c r="C4" t="n">
-        <v>10405</v>
+        <v>3912</v>
       </c>
       <c r="D4" t="n">
-        <v>11757</v>
+        <v>9911</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1048</v>
+        <v>305</v>
       </c>
       <c r="C5" t="n">
-        <v>13052</v>
+        <v>3514</v>
       </c>
       <c r="D5" t="n">
-        <v>5600</v>
+        <v>7301</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="C6" t="n">
-        <v>8074</v>
+        <v>4803</v>
       </c>
       <c r="D6" t="n">
-        <v>1803</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>70</v>
+        <v>208</v>
       </c>
       <c r="C7" t="n">
-        <v>3605</v>
+        <v>5098</v>
       </c>
       <c r="D7" t="n">
-        <v>504</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>1261</v>
+        <v>3665</v>
       </c>
       <c r="D8" t="n">
-        <v>289</v>
+        <v>509</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>345</v>
+        <v>1752</v>
       </c>
       <c r="D9" t="n">
-        <v>175</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>591</v>
       </c>
       <c r="D10" t="n">
-        <v>131</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5706</v>
+        <v>3571</v>
       </c>
       <c r="C2" t="n">
-        <v>9233</v>
+        <v>8513</v>
       </c>
       <c r="D2" t="n">
-        <v>14664</v>
+        <v>21993</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2116</v>
+        <v>840</v>
       </c>
       <c r="C3" t="n">
-        <v>7361</v>
+        <v>3439</v>
       </c>
       <c r="D3" t="n">
-        <v>2767</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3753</v>
+        <v>1903</v>
       </c>
       <c r="C2" t="n">
-        <v>6484</v>
+        <v>6303</v>
       </c>
       <c r="D2" t="n">
-        <v>18982</v>
+        <v>26643</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3211</v>
+        <v>1871</v>
       </c>
       <c r="C3" t="n">
-        <v>7261</v>
+        <v>5582</v>
       </c>
       <c r="D3" t="n">
-        <v>4562</v>
+        <v>6081</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>953</v>
+        <v>415</v>
       </c>
       <c r="C4" t="n">
-        <v>4356</v>
+        <v>2193</v>
       </c>
       <c r="D4" t="n">
-        <v>1739</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>343</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4692</v>
+        <v>1341</v>
       </c>
       <c r="C2" t="n">
-        <v>10179</v>
+        <v>4284</v>
       </c>
       <c r="D2" t="n">
-        <v>21306</v>
+        <v>31617</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2863</v>
+        <v>1556</v>
       </c>
       <c r="C3" t="n">
-        <v>5936</v>
+        <v>5162</v>
       </c>
       <c r="D3" t="n">
-        <v>6540</v>
+        <v>9087</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1743</v>
+        <v>1005</v>
       </c>
       <c r="C4" t="n">
-        <v>5882</v>
+        <v>4164</v>
       </c>
       <c r="D4" t="n">
-        <v>2228</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>445</v>
+        <v>224</v>
       </c>
       <c r="C5" t="n">
-        <v>2438</v>
+        <v>1346</v>
       </c>
       <c r="D5" t="n">
-        <v>1260</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5880</v>
+        <v>932</v>
       </c>
       <c r="C2" t="n">
-        <v>7044</v>
+        <v>4744</v>
       </c>
       <c r="D2" t="n">
-        <v>30346</v>
+        <v>29024</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3043</v>
+        <v>1201</v>
       </c>
       <c r="C3" t="n">
-        <v>7043</v>
+        <v>4053</v>
       </c>
       <c r="D3" t="n">
-        <v>8324</v>
+        <v>12037</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1953</v>
+        <v>1094</v>
       </c>
       <c r="C4" t="n">
-        <v>5788</v>
+        <v>4642</v>
       </c>
       <c r="D4" t="n">
-        <v>2946</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>887</v>
+        <v>522</v>
       </c>
       <c r="C5" t="n">
-        <v>4116</v>
+        <v>2860</v>
       </c>
       <c r="D5" t="n">
-        <v>1388</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>256</v>
+        <v>152</v>
       </c>
       <c r="C6" t="n">
-        <v>1367</v>
+        <v>828</v>
       </c>
       <c r="D6" t="n">
-        <v>935</v>
+        <v>845</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>374</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5556</v>
+        <v>1002</v>
       </c>
       <c r="C2" t="n">
-        <v>10652</v>
+        <v>8211</v>
       </c>
       <c r="D2" t="n">
-        <v>36507</v>
+        <v>26769</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3179</v>
+        <v>892</v>
       </c>
       <c r="C3" t="n">
-        <v>5779</v>
+        <v>3837</v>
       </c>
       <c r="D3" t="n">
-        <v>10261</v>
+        <v>13771</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1540</v>
+        <v>993</v>
       </c>
       <c r="C4" t="n">
-        <v>5231</v>
+        <v>4228</v>
       </c>
       <c r="D4" t="n">
-        <v>3273</v>
+        <v>5127</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>728</v>
+        <v>689</v>
       </c>
       <c r="C5" t="n">
-        <v>3619</v>
+        <v>3696</v>
       </c>
       <c r="D5" t="n">
-        <v>1308</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>265</v>
+        <v>293</v>
       </c>
       <c r="C6" t="n">
-        <v>1807</v>
+        <v>1852</v>
       </c>
       <c r="D6" t="n">
-        <v>759</v>
+        <v>919</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>616</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4461</v>
+        <v>1915</v>
       </c>
       <c r="C2" t="n">
-        <v>8282</v>
+        <v>11416</v>
       </c>
       <c r="D2" t="n">
-        <v>34916</v>
+        <v>27533</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3594</v>
+        <v>778</v>
       </c>
       <c r="C3" t="n">
-        <v>7361</v>
+        <v>5212</v>
       </c>
       <c r="D3" t="n">
-        <v>13915</v>
+        <v>14695</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2050</v>
+        <v>816</v>
       </c>
       <c r="C4" t="n">
-        <v>5443</v>
+        <v>3941</v>
       </c>
       <c r="D4" t="n">
-        <v>4582</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>992</v>
+        <v>739</v>
       </c>
       <c r="C5" t="n">
-        <v>4422</v>
+        <v>3844</v>
       </c>
       <c r="D5" t="n">
-        <v>1645</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>455</v>
+        <v>423</v>
       </c>
       <c r="C6" t="n">
-        <v>2794</v>
+        <v>2717</v>
       </c>
       <c r="D6" t="n">
-        <v>841</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C7" t="n">
-        <v>1233</v>
+        <v>1168</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>387</v>
+        <v>418</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4423</v>
+        <v>1657</v>
       </c>
       <c r="C2" t="n">
-        <v>9985</v>
+        <v>7032</v>
       </c>
       <c r="D2" t="n">
-        <v>30012</v>
+        <v>21647</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3300</v>
+        <v>1232</v>
       </c>
       <c r="C3" t="n">
-        <v>6819</v>
+        <v>8428</v>
       </c>
       <c r="D3" t="n">
-        <v>16127</v>
+        <v>16285</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2399</v>
+        <v>682</v>
       </c>
       <c r="C4" t="n">
-        <v>6308</v>
+        <v>6149</v>
       </c>
       <c r="D4" t="n">
-        <v>6101</v>
+        <v>5858</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1299</v>
+        <v>390</v>
       </c>
       <c r="C5" t="n">
-        <v>4869</v>
+        <v>2662</v>
       </c>
       <c r="D5" t="n">
-        <v>2130</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>642</v>
+        <v>161</v>
       </c>
       <c r="C6" t="n">
-        <v>3591</v>
+        <v>1144</v>
       </c>
       <c r="D6" t="n">
-        <v>968</v>
+        <v>637</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>266</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>2000</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>801</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>292</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
